--- a/VerveStacks_ESP_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ESP_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77670423-9462-4897-A230-0E6607E4C52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{033CE7FF-E6CE-4818-A211-356808EBFEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5509,7 +5509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5F15D6-2988-45D1-B753-AED98699845E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F1D1821-0498-47EC-8A67-575AFEC39E11}">
   <dimension ref="B2:AF891"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24834,7 +24834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA17284-0928-4173-89A6-8D359167F8C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741BFB99-EFD4-4D0A-AC6C-56263FE04EFD}">
   <dimension ref="B9:L67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
